--- a/Excel/BuffConfig.xlsx
+++ b/Excel/BuffConfig.xlsx
@@ -95,13 +95,13 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>重击</t>
+    <t>重击战法</t>
   </si>
   <si>
     <t>此次攻击有{0}%的概率使伤害提高{1}%</t>
   </si>
   <si>
-    <t>暴击</t>
+    <t>弱点追踪</t>
   </si>
   <si>
     <t>如果此次攻击触发暴击，此次伤害提高{1}%</t>
@@ -135,7 +135,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +154,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -636,143 +642,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1160,14 +1167,14 @@
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
@@ -1177,7 +1184,7 @@
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="2">
@@ -1197,10 +1204,10 @@
       <c r="D8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -1570,7 +1577,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D3 E3 F3 C4:D4 E4 F4 C5:E5 F5 G3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
